--- a/Table12_ComparisonSummary.xlsx
+++ b/Table12_ComparisonSummary.xlsx
@@ -463,7 +463,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>0.121</t>
+          <t>0.084</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -473,12 +473,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>[0.073, 0.170]</t>
+          <t>[0.000, 0.151]</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Table 8</t>
+          <t>Table 10</t>
         </is>
       </c>
     </row>
@@ -527,7 +527,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>0.081</t>
+          <t>0.047</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -537,7 +537,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>[-0.002, 0.179]</t>
+          <t>[-0.071, 0.149]</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -591,7 +591,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>0.073</t>
+          <t>0.042</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -601,7 +601,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>[-0.023, 0.175]</t>
+          <t>[-0.083, 0.147]</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">

--- a/Table12_ComparisonSummary.xlsx
+++ b/Table12_ComparisonSummary.xlsx
@@ -463,7 +463,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>0.084</t>
+          <t>0.122</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -473,7 +473,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>[0.000, 0.151]</t>
+          <t>[0.073, 0.171]</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -527,7 +527,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>0.047</t>
+          <t>0.053</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -537,7 +537,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>[-0.071, 0.149]</t>
+          <t>[-0.027, 0.144]</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -591,7 +591,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>0.042</t>
+          <t>0.046</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -601,7 +601,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>[-0.083, 0.147]</t>
+          <t>[-0.046, 0.141]</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
